--- a/xlsxtemplate/chathai-templateV.1.0.0.xlsx
+++ b/xlsxtemplate/chathai-templateV.1.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khongEM\chathai\Chathai_OnDev\xlsxtemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Chathai_OnDev\xlsxtemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77244FF7-D82E-4438-8519-75C4F72C3D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1F9FF7-59EE-4328-9256-17745255492C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <si>
     <t>TestScenario(des)</t>
   </si>
@@ -70,9 +70,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>Learn Cypress'</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -86,6 +83,18 @@
   </si>
   <si>
     <t>Learn Cypress</t>
+  </si>
+  <si>
+    <t>beforeEach</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>skip</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -450,8 +459,12 @@
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
@@ -470,8 +483,12 @@
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
@@ -490,16 +507,20 @@
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
@@ -512,13 +533,17 @@
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -532,14 +557,18 @@
       <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
@@ -552,13 +581,17 @@
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="5"/>
     </row>
